--- a/output/graficos_nacionales/plot_nacional_serie_i_peringrmin_s_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_peringrmin_s_2023.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:21</t>
+    <t xml:space="preserve">2026-10-05 19:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
